--- a/Team-Data/2011-12/4-12-2011-12.xlsx
+++ b/Team-Data/2011-12/4-12-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -778,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>2.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -954,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>28</v>
@@ -981,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1025,25 +1092,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="J4" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K4" t="n">
         <v>0.418</v>
@@ -1052,34 +1119,34 @@
         <v>4.1</v>
       </c>
       <c r="M4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.304</v>
+        <v>0.301</v>
       </c>
       <c r="O4" t="n">
         <v>16.6</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
         <v>0.752</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S4" t="n">
         <v>28.8</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U4" t="n">
         <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W4" t="n">
         <v>6.3</v>
@@ -1088,19 +1155,19 @@
         <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
         <v>88.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.3</v>
+        <v>-13.1</v>
       </c>
       <c r="AD4" t="n">
         <v>27</v>
@@ -1115,7 +1182,7 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1145,16 +1212,16 @@
         <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1163,7 +1230,7 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>24</v>
@@ -1172,7 +1239,7 @@
         <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1207,37 +1274,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.763</v>
+        <v>0.759</v>
       </c>
       <c r="H5" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I5" t="n">
         <v>37.5</v>
       </c>
       <c r="J5" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M5" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
         <v>15.5</v>
@@ -1246,10 +1313,10 @@
         <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="R5" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="S5" t="n">
         <v>32.3</v>
@@ -1258,19 +1325,19 @@
         <v>46.3</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W5" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z5" t="n">
         <v>17.2</v>
@@ -1285,7 +1352,7 @@
         <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,13 +1364,13 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
         <v>10</v>
@@ -1318,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1339,7 +1406,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1357,7 +1424,7 @@
         <v>28</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-6</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1482,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
         <v>15</v>
@@ -1503,7 +1570,7 @@
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1638,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
         <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.552</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J7" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L7" t="n">
         <v>7.4</v>
       </c>
       <c r="M7" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O7" t="n">
         <v>15.3</v>
@@ -1613,19 +1680,19 @@
         <v>0.756</v>
       </c>
       <c r="R7" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T7" t="n">
         <v>42.6</v>
       </c>
       <c r="U7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
         <v>8.6</v>
@@ -1637,19 +1704,19 @@
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
@@ -1661,7 +1728,7 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
         <v>19</v>
@@ -1670,7 +1737,7 @@
         <v>14</v>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1694,16 +1761,16 @@
         <v>28</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
         <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1718,7 +1785,7 @@
         <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>20</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1831,25 +1898,25 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
@@ -1861,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>0.379</v>
+        <v>0.368</v>
       </c>
       <c r="H9" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="J9" t="n">
         <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L9" t="n">
         <v>4.5</v>
@@ -1965,7 +2032,7 @@
         <v>13.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>16.7</v>
@@ -1974,7 +2041,7 @@
         <v>22.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
@@ -1983,52 +2050,52 @@
         <v>28</v>
       </c>
       <c r="T9" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U9" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA9" t="n">
         <v>19.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.3</v>
+        <v>-5.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
         <v>14</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AJ9" t="n">
         <v>25</v>
@@ -2064,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="AU9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
@@ -2082,13 +2149,13 @@
         <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -2117,22 +2184,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J10" t="n">
         <v>82.2</v>
@@ -2144,19 +2211,19 @@
         <v>8.1</v>
       </c>
       <c r="M10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.389</v>
       </c>
       <c r="O10" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P10" t="n">
         <v>19.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R10" t="n">
         <v>9.699999999999999</v>
@@ -2165,25 +2232,25 @@
         <v>29.3</v>
       </c>
       <c r="T10" t="n">
-        <v>39.1</v>
+        <v>38.9</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V10" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W10" t="n">
         <v>8.1</v>
       </c>
       <c r="X10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y10" t="n">
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA10" t="n">
         <v>16.8</v>
@@ -2192,10 +2259,10 @@
         <v>98.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2243,7 +2310,7 @@
         <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2255,7 +2322,7 @@
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
@@ -2267,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2398,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>12</v>
@@ -2410,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
         <v>27</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2619,7 +2686,7 @@
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.603</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,7 +2748,7 @@
         <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K13" t="n">
         <v>0.452</v>
@@ -2690,19 +2757,19 @@
         <v>7.6</v>
       </c>
       <c r="M13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O13" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>12.2</v>
@@ -2711,13 +2778,13 @@
         <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U13" t="n">
         <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W13" t="n">
         <v>8.300000000000001</v>
@@ -2732,19 +2799,19 @@
         <v>21.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB13" t="n">
         <v>97.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2753,16 +2820,16 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2774,7 +2841,7 @@
         <v>13</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2792,10 +2859,10 @@
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>7</v>
@@ -2804,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2813,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2983,7 +3050,7 @@
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
         <v>5</v>
@@ -2992,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
         <v>17</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -3027,43 +3094,43 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" t="n">
         <v>34</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.586</v>
+        <v>0.596</v>
       </c>
       <c r="H15" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I15" t="n">
         <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
         <v>4.1</v>
       </c>
       <c r="M15" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.326</v>
+        <v>0.329</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0.756</v>
@@ -3087,13 +3154,13 @@
         <v>9.699999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA15" t="n">
         <v>19.5</v>
@@ -3102,16 +3169,16 @@
         <v>95.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
         <v>8</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG15" t="n">
         <v>8</v>
@@ -3120,7 +3187,7 @@
         <v>14</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>9</v>
@@ -3135,7 +3202,7 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3156,7 +3223,7 @@
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="n">
         <v>15</v>
@@ -3174,13 +3241,13 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB15" t="n">
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="n">
         <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.702</v>
+        <v>0.714</v>
       </c>
       <c r="H16" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I16" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.473</v>
+        <v>0.474</v>
       </c>
       <c r="L16" t="n">
         <v>5.7</v>
@@ -3242,13 +3309,13 @@
         <v>0.369</v>
       </c>
       <c r="O16" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R16" t="n">
         <v>10.4</v>
@@ -3263,46 +3330,46 @@
         <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>9.1</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y16" t="n">
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.1</v>
+        <v>100.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="AD16" t="n">
         <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3320,13 +3387,13 @@
         <v>5</v>
       </c>
       <c r="AO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" t="n">
         <v>5</v>
       </c>
-      <c r="AP16" t="n">
-        <v>8</v>
-      </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3338,16 +3405,16 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.417</v>
+        <v>0.424</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
@@ -3591,7 +3658,7 @@
         <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.435</v>
@@ -3603,16 +3670,16 @@
         <v>21.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P18" t="n">
         <v>25.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
@@ -3630,25 +3697,25 @@
         <v>15.3</v>
       </c>
       <c r="W18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA18" t="n">
         <v>21.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="AD18" t="n">
         <v>1</v>
@@ -3675,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3684,13 +3751,13 @@
         <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP18" t="n">
         <v>6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -3833,10 +3900,10 @@
         <v>-5.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>25</v>
@@ -3902,13 +3969,13 @@
         <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4084,7 +4151,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>17</v>
@@ -4209,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4221,7 +4288,7 @@
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
@@ -4248,7 +4315,7 @@
         <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
         <v>29</v>
@@ -4260,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>11</v>
@@ -4430,7 +4497,7 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4561,19 +4628,19 @@
         <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE23" t="n">
         <v>8</v>
       </c>
       <c r="AF23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4582,7 +4649,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4630,13 +4697,13 @@
         <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4755,7 +4822,7 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>17</v>
@@ -4940,7 +5007,7 @@
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -4958,7 +5025,7 @@
         <v>17</v>
       </c>
       <c r="AO25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4994,7 +5061,7 @@
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>0.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5170,7 +5237,7 @@
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5343,7 +5410,7 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
@@ -5361,7 +5428,7 @@
         <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.719</v>
+        <v>0.714</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
@@ -5411,43 +5478,43 @@
         <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>82.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.387</v>
+        <v>0.388</v>
       </c>
       <c r="O28" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.737</v>
+        <v>0.735</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S28" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T28" t="n">
         <v>42.5</v>
       </c>
       <c r="U28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V28" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W28" t="n">
         <v>7.3</v>
@@ -5456,19 +5523,19 @@
         <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z28" t="n">
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.8</v>
+        <v>101.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD28" t="n">
         <v>27</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5504,16 +5571,16 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
         <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
         <v>6</v>
@@ -5525,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW28" t="n">
         <v>20</v>
@@ -5534,13 +5601,13 @@
         <v>24</v>
       </c>
       <c r="AY28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ28" t="n">
         <v>3</v>
       </c>
       <c r="BA28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>25</v>
@@ -5665,16 +5732,16 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5871,7 +5938,7 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>23</v>
@@ -6050,7 +6117,7 @@
         <v>25</v>
       </c>
       <c r="AO31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
@@ -6086,7 +6153,7 @@
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-12-2011-12</t>
+          <t>2012-04-12</t>
         </is>
       </c>
     </row>
